--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -5196,11 +5196,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5319,11 +5315,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -5443,11 +5435,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5566,11 +5554,7 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -5690,11 +5674,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5930,11 +5910,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6052,11 +6028,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6174,11 +6146,7 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6413,11 +6381,7 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6535,11 +6499,7 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6659,11 +6619,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6782,11 +6738,7 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -6904,11 +6856,7 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -7028,11 +6976,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7151,11 +7095,7 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -7390,11 +7330,7 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -7514,11 +7450,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7871,11 +7803,7 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -7993,11 +7921,7 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -8115,11 +8039,7 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -8237,11 +8157,7 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gotland, Jmt</t>
@@ -8361,11 +8277,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8603,11 +8515,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8852,11 +8760,7 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>137245438</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>137245443</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>137245458</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>137245461</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137245501</v>
       </c>
       <c r="B46" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>137245507</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>137245509</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>137245512</v>
       </c>
       <c r="B49" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137245513</v>
       </c>
       <c r="B50" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>137245517</v>
       </c>
       <c r="B51" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137245522</v>
       </c>
       <c r="B52" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>137245523</v>
       </c>
       <c r="B53" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>137245526</v>
       </c>
       <c r="B54" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>137245528</v>
       </c>
       <c r="B55" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>137245530</v>
       </c>
       <c r="B56" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137245534</v>
       </c>
       <c r="B57" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>137245538</v>
       </c>
       <c r="B58" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>137245539</v>
       </c>
       <c r="B59" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>137245540</v>
       </c>
       <c r="B60" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>137245543</v>
       </c>
       <c r="B61" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>137245547</v>
       </c>
       <c r="B62" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>137245555</v>
       </c>
       <c r="B63" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>137245556</v>
       </c>
       <c r="B64" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137245559</v>
       </c>
       <c r="B65" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>137245571</v>
       </c>
       <c r="B66" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>137245575</v>
       </c>
       <c r="B67" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>137245576</v>
       </c>
       <c r="B68" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137245581</v>
       </c>
       <c r="B69" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137245585</v>
       </c>
       <c r="B70" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>137245371</v>
       </c>
       <c r="B71" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>137245454</v>
       </c>
       <c r="B72" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>137245438</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>137245443</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>137245458</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>137245461</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137245501</v>
       </c>
       <c r="B46" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>137245507</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>137245509</v>
       </c>
       <c r="B48" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>137245512</v>
       </c>
       <c r="B49" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137245513</v>
       </c>
       <c r="B50" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>137245517</v>
       </c>
       <c r="B51" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137245522</v>
       </c>
       <c r="B52" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>137245523</v>
       </c>
       <c r="B53" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>137245526</v>
       </c>
       <c r="B54" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>137245528</v>
       </c>
       <c r="B55" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>137245530</v>
       </c>
       <c r="B56" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137245534</v>
       </c>
       <c r="B57" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>137245538</v>
       </c>
       <c r="B58" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>137245539</v>
       </c>
       <c r="B59" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>137245540</v>
       </c>
       <c r="B60" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>137245543</v>
       </c>
       <c r="B61" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>137245547</v>
       </c>
       <c r="B62" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>137245555</v>
       </c>
       <c r="B63" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>137245556</v>
       </c>
       <c r="B64" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137245559</v>
       </c>
       <c r="B65" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>137245571</v>
       </c>
       <c r="B66" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>137245575</v>
       </c>
       <c r="B67" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>137245576</v>
       </c>
       <c r="B68" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137245581</v>
       </c>
       <c r="B69" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137245585</v>
       </c>
       <c r="B70" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>137245371</v>
       </c>
       <c r="B71" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>137245454</v>
       </c>
       <c r="B72" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>137245438</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>137245443</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>137245458</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>137245461</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137245501</v>
       </c>
       <c r="B46" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>137245507</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>137245509</v>
       </c>
       <c r="B48" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>137245512</v>
       </c>
       <c r="B49" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137245513</v>
       </c>
       <c r="B50" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>137245517</v>
       </c>
       <c r="B51" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137245522</v>
       </c>
       <c r="B52" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>137245523</v>
       </c>
       <c r="B53" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>137245526</v>
       </c>
       <c r="B54" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>137245528</v>
       </c>
       <c r="B55" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>137245530</v>
       </c>
       <c r="B56" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137245534</v>
       </c>
       <c r="B57" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>137245538</v>
       </c>
       <c r="B58" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>137245539</v>
       </c>
       <c r="B59" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>137245540</v>
       </c>
       <c r="B60" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>137245543</v>
       </c>
       <c r="B61" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>137245547</v>
       </c>
       <c r="B62" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>137245555</v>
       </c>
       <c r="B63" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>137245556</v>
       </c>
       <c r="B64" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137245559</v>
       </c>
       <c r="B65" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>137245571</v>
       </c>
       <c r="B66" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>137245575</v>
       </c>
       <c r="B67" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>137245576</v>
       </c>
       <c r="B68" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137245581</v>
       </c>
       <c r="B69" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137245585</v>
       </c>
       <c r="B70" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>137245454</v>
       </c>
       <c r="B72" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/S 2432-2026 artfynd.xlsx
+++ b/artfynd/S 2432-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137245367</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137245410</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137245466</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137245434</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137245566</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137245579</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137245568</v>
       </c>
       <c r="B8" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137245535</v>
       </c>
       <c r="B9" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137245368</v>
       </c>
       <c r="B10" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137245370</v>
       </c>
       <c r="B11" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137245379</v>
       </c>
       <c r="B12" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137245384</v>
       </c>
       <c r="B13" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137245415</v>
       </c>
       <c r="B14" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137245491</v>
       </c>
       <c r="B15" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137245381</v>
       </c>
       <c r="B16" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137245416</v>
       </c>
       <c r="B17" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137245389</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>137245404</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>137245436</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>137245452</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137245486</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137245499</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137245567</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>137245352</v>
       </c>
       <c r="B25" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137245353</v>
       </c>
       <c r="B26" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>137245355</v>
       </c>
       <c r="B27" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137245364</v>
       </c>
       <c r="B28" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137245432</v>
       </c>
       <c r="B29" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137245448</v>
       </c>
       <c r="B30" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137245450</v>
       </c>
       <c r="B31" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137245451</v>
       </c>
       <c r="B32" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>137245456</v>
       </c>
       <c r="B33" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>137245462</v>
       </c>
       <c r="B34" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>137245463</v>
       </c>
       <c r="B35" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137245471</v>
       </c>
       <c r="B36" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>137245473</v>
       </c>
       <c r="B37" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>137245524</v>
       </c>
       <c r="B38" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>137245553</v>
       </c>
       <c r="B39" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>137245562</v>
       </c>
       <c r="B40" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137245569</v>
       </c>
       <c r="B41" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>137245438</v>
       </c>
       <c r="B42" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>137245443</v>
       </c>
       <c r="B43" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>137245458</v>
       </c>
       <c r="B44" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>137245461</v>
       </c>
       <c r="B45" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>137245501</v>
       </c>
       <c r="B46" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>137245507</v>
       </c>
       <c r="B47" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>137245509</v>
       </c>
       <c r="B48" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>137245512</v>
       </c>
       <c r="B49" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>137245513</v>
       </c>
       <c r="B50" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>137245517</v>
       </c>
       <c r="B51" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>137245522</v>
       </c>
       <c r="B52" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>137245523</v>
       </c>
       <c r="B53" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>137245526</v>
       </c>
       <c r="B54" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>137245528</v>
       </c>
       <c r="B55" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>137245530</v>
       </c>
       <c r="B56" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137245534</v>
       </c>
       <c r="B57" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>137245538</v>
       </c>
       <c r="B58" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>137245539</v>
       </c>
       <c r="B59" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>137245540</v>
       </c>
       <c r="B60" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>137245543</v>
       </c>
       <c r="B61" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>137245547</v>
       </c>
       <c r="B62" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>137245555</v>
       </c>
       <c r="B63" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>137245556</v>
       </c>
       <c r="B64" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>137245559</v>
       </c>
       <c r="B65" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>137245571</v>
       </c>
       <c r="B66" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>137245575</v>
       </c>
       <c r="B67" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>137245576</v>
       </c>
       <c r="B68" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>137245581</v>
       </c>
       <c r="B69" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137245585</v>
       </c>
       <c r="B70" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>137245371</v>
       </c>
       <c r="B71" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>137245454</v>
       </c>
       <c r="B72" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>137245408</v>
       </c>
       <c r="B75" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>137245350</v>
       </c>
       <c r="B76" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>137245358</v>
       </c>
       <c r="B77" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>137245362</v>
       </c>
       <c r="B78" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>137245372</v>
       </c>
       <c r="B79" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>137245395</v>
       </c>
       <c r="B80" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>137245401</v>
       </c>
       <c r="B81" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>137245411</v>
       </c>
       <c r="B82" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>137245546</v>
       </c>
       <c r="B83" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>137245373</v>
       </c>
       <c r="B87" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>137245376</v>
       </c>
       <c r="B88" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>137245380</v>
       </c>
       <c r="B89" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>137245394</v>
       </c>
       <c r="B90" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>137245397</v>
       </c>
       <c r="B91" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>137245405</v>
       </c>
       <c r="B92" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>137245407</v>
       </c>
       <c r="B93" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>137245413</v>
       </c>
       <c r="B94" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>137245421</v>
       </c>
       <c r="B95" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>137245426</v>
       </c>
       <c r="B96" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137245554</v>
       </c>
       <c r="B97" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137245582</v>
       </c>
       <c r="B98" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137245442</v>
       </c>
       <c r="B99" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
